--- a/EKG_Kalite_Yönetim_Sistemi/07_Standart İş ve Uygunsuz Ürün/01_SW1 - Standart İş, İş Yeri ve Görsel Yönetim/EKG-URT-FRM-07_5s_degerlendirme_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/07_Standart İş ve Uygunsuz Ürün/01_SW1 - Standart İş, İş Yeri ve Görsel Yönetim/EKG-URT-FRM-07_5s_degerlendirme_formu.xlsx
@@ -1079,7 +1079,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-FRM-07&amp;C&amp;"Arial,Regular"&amp;11 5S Değerlendirme Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Uygulanamaz kodu NA yapıldı; mevcut cam odaklı sorular ve kanıtlı faaliyet sayfası korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25d7ca649bbe4b20"/>
   <x:tableParts count="1">
@@ -1416,7 +1417,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-FRM-07&amp;C&amp;"Arial,Regular"&amp;11 5S Değerlendirme Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Uygulanamaz kodu NA yapıldı; mevcut cam odaklı sorular ve kanıtlı faaliyet sayfası korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80acb90ce7e4445d"/>
   <x:tableParts count="1">
